--- a/Proyectos/Proyecto8 - Funciones Adicionales de Power BI/Recursos/1+-+Ejemplos/E2.xlsx
+++ b/Proyectos/Proyecto8 - Funciones Adicionales de Power BI/Recursos/1+-+Ejemplos/E2.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\1 - Ejemplos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\root\Computacion\Data\Analytics\Udemy\Power BI\Curso Power BI – Análisis de Datos y Business Intelligence\Proyectos\Proyecto8 - Funciones Adicionales de Power BI\Recursos\1+-+Ejemplos\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2647E9CF-83A9-4D71-A08C-96E78FADA6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="9576"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="9" r:id="rId1"/>
@@ -189,7 +190,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -507,7 +508,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -701,13 +702,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
-      </left>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color theme="1" tint="0.499984740745262"/>
       </bottom>
@@ -718,9 +724,7 @@
       <right style="thin">
         <color theme="1" tint="0.499984740745262"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color theme="1" tint="0.499984740745262"/>
       </bottom>
@@ -729,90 +733,10 @@
     <border>
       <left/>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color theme="1" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color theme="0" tint="-0.34998626667073579"/>
       </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -823,9 +747,7 @@
       <top style="thin">
         <color theme="0" tint="-0.34998626667073579"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -838,42 +760,7 @@
       <top style="thin">
         <color theme="0" tint="-0.34998626667073579"/>
       </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -921,76 +808,1471 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Énfasis6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Énfasis6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Énfasis6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Bueno" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Cálculo" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Celda de comprobación" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Celda vinculada" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Encabezado 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Encabezado 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Énfasis1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Énfasis2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Énfasis3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Énfasis4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Énfasis5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Énfasis6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Entrada" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Incorrecto" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Notas" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Salida" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Texto de advertencia" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Texto explicativo" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Título" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Título 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="85">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="1" tint="0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color theme="1" tint="0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="1" tint="0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color theme="1" tint="0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="1" tint="0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color theme="1" tint="0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="1" tint="0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color theme="1" tint="0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/m/yyyy"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.44999542222357858"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="1" tint="0.499984740745262"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.34998626667073579"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color theme="1" tint="0.499984740745262"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1001,6 +2283,121 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7808860C-C3B8-4786-BA39-E9D406936F26}" name="Tabla2014" displayName="Tabla2014" ref="B3:O34" totalsRowShown="0" headerRowDxfId="68" headerRowBorderDxfId="83" tableBorderDxfId="84">
+  <autoFilter ref="B3:O34" xr:uid="{7808860C-C3B8-4786-BA39-E9D406936F26}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{2D6F6A95-8115-494B-8E76-C03685EFD93E}" name="Año" dataDxfId="82"/>
+    <tableColumn id="2" xr3:uid="{E14BEF4C-DF14-4627-AEC8-F17FC32B40E3}" name="Genero" dataDxfId="81"/>
+    <tableColumn id="3" xr3:uid="{D05936F3-ECAA-451D-AD12-984917E57E2A}" name="ene" dataDxfId="80"/>
+    <tableColumn id="4" xr3:uid="{F84F0027-A3A3-49F0-BB90-8F060D614532}" name="feb" dataDxfId="79"/>
+    <tableColumn id="5" xr3:uid="{759C9BC4-E44A-4541-916E-A23AE71C4BA0}" name="mar" dataDxfId="78"/>
+    <tableColumn id="6" xr3:uid="{8CE02D6E-A105-4F0A-9D3B-34D9CBCC5BD6}" name="abr" dataDxfId="77"/>
+    <tableColumn id="7" xr3:uid="{2CA5DAC5-1CF4-45D9-BD80-09871ADDDBC9}" name="may" dataDxfId="76"/>
+    <tableColumn id="8" xr3:uid="{822DD6B4-EEAD-4A8C-A9BC-D208878C8B23}" name="jun" dataDxfId="75"/>
+    <tableColumn id="9" xr3:uid="{1E355A07-2390-4851-8627-124CAE964440}" name="jul" dataDxfId="74"/>
+    <tableColumn id="10" xr3:uid="{901FE7DC-969E-4F13-B4CD-B7562437BEC1}" name="ago" dataDxfId="73"/>
+    <tableColumn id="11" xr3:uid="{2CA63AEA-FED8-44BF-9860-26F573C20F40}" name="sep" dataDxfId="72"/>
+    <tableColumn id="12" xr3:uid="{38A0CBC6-CA39-4EC1-83E2-BF3EFF4C014F}" name="oct" dataDxfId="71"/>
+    <tableColumn id="13" xr3:uid="{C005C947-3937-4BA4-8760-8FB993934C20}" name="nov" dataDxfId="70"/>
+    <tableColumn id="14" xr3:uid="{8C254A47-9C06-4087-A76B-25C1B98846A3}" name="dic" dataDxfId="69"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FFC5E5CE-30F1-43D8-89A6-0B848A57703C}" name="Tabla2015" displayName="Tabla2015" ref="B37:O66" totalsRowShown="0" headerRowDxfId="51" headerRowBorderDxfId="66" tableBorderDxfId="67">
+  <autoFilter ref="B37:O66" xr:uid="{FFC5E5CE-30F1-43D8-89A6-0B848A57703C}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{7B67AAA1-ED8E-4E7C-866F-7A32DDC1AE48}" name="Año" dataDxfId="65"/>
+    <tableColumn id="2" xr3:uid="{6CAD03D2-2668-44C3-BD99-B993CB546EBD}" name="Genero" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{055D01F2-0AE9-412A-AA9D-9D544BF6DF7C}" name="ene" dataDxfId="63"/>
+    <tableColumn id="4" xr3:uid="{E90A3D18-0B51-4DDF-816D-AEB3D7C79EB4}" name="feb" dataDxfId="62"/>
+    <tableColumn id="5" xr3:uid="{984663D0-D196-4898-B93A-18B335A5B49F}" name="mar" dataDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{72B51821-D273-4054-8091-D092273489AC}" name="abr" dataDxfId="60"/>
+    <tableColumn id="7" xr3:uid="{9F358AED-06B6-41D1-B9B8-B1243539FEEA}" name="may" dataDxfId="59"/>
+    <tableColumn id="8" xr3:uid="{881A6C8E-B2E3-4CA3-8D63-1C3754297EC3}" name="jun" dataDxfId="58"/>
+    <tableColumn id="9" xr3:uid="{090D6C02-B237-403D-8972-366E0CDC8600}" name="jul" dataDxfId="57"/>
+    <tableColumn id="10" xr3:uid="{117678BC-4198-4199-8E8B-3C6D0F75D9BD}" name="ago" dataDxfId="56"/>
+    <tableColumn id="11" xr3:uid="{BE84B487-F84B-43A5-8479-BF8E262A2740}" name="sep" dataDxfId="55"/>
+    <tableColumn id="12" xr3:uid="{6D44A453-DF65-4BFA-BD99-CA1AC4736288}" name="oct" dataDxfId="54"/>
+    <tableColumn id="13" xr3:uid="{B7BAF735-5F8B-42A5-A184-9F0F703CA9BD}" name="nov" dataDxfId="53"/>
+    <tableColumn id="14" xr3:uid="{16629299-48DB-4B2F-BAA8-BE4F4BB3833A}" name="dic" dataDxfId="52"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8DA8A9B7-0A23-4955-BF12-B6FF55A292F2}" name="Tabla2016" displayName="Tabla2016" ref="B69:O103" totalsRowShown="0" headerRowDxfId="34" headerRowBorderDxfId="49" tableBorderDxfId="50">
+  <autoFilter ref="B69:O103" xr:uid="{8DA8A9B7-0A23-4955-BF12-B6FF55A292F2}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{201A692C-066E-432A-A3EA-4C83F2D012D9}" name="Año" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{C463E50E-36B4-43A1-B304-F08DFB0A1223}" name="Genero" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{CDB76492-77FF-491F-941D-E96322991E2F}" name="ene" dataDxfId="46"/>
+    <tableColumn id="4" xr3:uid="{91D7DF2E-00A8-49D6-8092-D42F65067808}" name="feb" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{A3901F4F-A27D-4349-A039-59D41AF87085}" name="mar" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{F858379E-9AD9-4D59-B1B3-D978CF798A66}" name="abr" dataDxfId="43"/>
+    <tableColumn id="7" xr3:uid="{E7A5A0C0-9DC9-4FE2-A1E6-5637DFEC4A18}" name="may" dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{F8884341-D5B3-4CF4-B8E9-1420918964AD}" name="jun" dataDxfId="41"/>
+    <tableColumn id="9" xr3:uid="{DB5DED2C-93FB-4984-B6C8-4D4C1C727182}" name="jul" dataDxfId="40"/>
+    <tableColumn id="10" xr3:uid="{EB2FD94B-1CF6-4774-BA25-DD61F29A4C94}" name="ago" dataDxfId="39"/>
+    <tableColumn id="11" xr3:uid="{399FF594-3E10-4F9B-90B3-453ED03C7F6A}" name="sep" dataDxfId="38"/>
+    <tableColumn id="12" xr3:uid="{83448BE2-B46C-4FDC-93B5-8EB236EF2273}" name="oct" dataDxfId="37"/>
+    <tableColumn id="13" xr3:uid="{494C1761-DBDD-488F-842F-06AF68685320}" name="nov" dataDxfId="36"/>
+    <tableColumn id="14" xr3:uid="{36750BFE-EF60-488B-BFD2-BF3721919F1C}" name="dic" dataDxfId="35"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{43EBF9A8-E4C2-456A-8450-C3B62C3BCFCE}" name="Tabla2017" displayName="Tabla2017" ref="B106:O140" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="32" tableBorderDxfId="33">
+  <autoFilter ref="B106:O140" xr:uid="{43EBF9A8-E4C2-456A-8450-C3B62C3BCFCE}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{6AB094B5-F84A-431B-A676-36734DB0B581}" name="Año" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{DFE89786-8990-4D96-8CDD-A7BB972A7066}" name="Genero" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{750D5D89-A600-4F90-AF72-5D502E2699E2}" name="ene" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{8423B741-9712-4E5B-B423-AE5754C15493}" name="feb" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{020CF684-AACE-4362-9D4D-3E0BA163F9F6}" name="mar" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{19CB7ADD-9D13-4F4A-BE4A-A574331D78A6}" name="abr" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{1F64BF82-1C22-4921-A916-E078F0EF7B82}" name="may" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{2984CF3F-A128-4999-ADE5-295166E464C2}" name="jun" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{A18178F4-6450-4F8C-A9DF-DC28DB0CABBF}" name="jul" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{66705C8F-A200-4E12-B98B-6AC48D5FA261}" name="ago" dataDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{FF79ED8C-E552-4667-83E0-0DCB712B7B24}" name="sep" dataDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{7B742C5E-CE33-4F5F-8408-E485B479B423}" name="oct" dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{7DA34EE3-1920-4F23-9649-FAD19A65C628}" name="nov" dataDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{83F5815C-D0B1-4696-A4B9-19378FB16487}" name="dic" dataDxfId="18"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{3D28F70D-4858-4A1F-8BB0-358C2D280352}" name="Tabla2018" displayName="Tabla2018" ref="B143:O176" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="15" tableBorderDxfId="16">
+  <autoFilter ref="B143:O176" xr:uid="{3D28F70D-4858-4A1F-8BB0-358C2D280352}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{5364DAD0-2AC3-433B-A743-94092A09E50D}" name="Año" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{CDBE2210-014E-4C7C-A7E0-C61CD78352B6}" name="Genero" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{75B74168-0399-4F45-B3A3-8C01EFD5F33D}" name="ene" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{52E63468-89F9-4C78-ADA1-4579E4C7B3E3}" name="feb" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{B3D9F3AB-FB2D-4E51-BC26-D5A6BEB5BD17}" name="mar" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{7604B98E-06BC-4F2A-B854-444811F713DB}" name="abr" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{1F761A9E-98A8-446A-87E9-14FAE53D32F8}" name="may" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{6B5E118B-808E-434B-869C-177222AEF55F}" name="jun" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{23C6FDE9-EC0F-4036-89BD-83A0D1EEE0C2}" name="jul" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{FCEE4C54-A4B0-4AED-A5B4-16C546553D1F}" name="ago" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{0FB8B889-E9F0-4B81-83EF-F7F3E03A2FFD}" name="sep" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{17DA54E6-0C66-427B-A7DB-ADE958343F18}" name="oct" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{D31FE8C3-AD4B-4EB7-B1EB-F073879948AF}" name="nov" dataDxfId="2"/>
+    <tableColumn id="14" xr3:uid="{FAE7D443-FC87-46E4-ADE8-68D465335513}" name="dic" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1265,90 +2662,90 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:O176"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.21875" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="18"/>
-    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875"/>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" customWidth="1"/>
+    <col min="7" max="7" width="6" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" customWidth="1"/>
+    <col min="9" max="9" width="6" customWidth="1"/>
+    <col min="10" max="10" width="5.42578125" customWidth="1"/>
+    <col min="11" max="12" width="6.28515625" customWidth="1"/>
+    <col min="13" max="13" width="5.85546875" customWidth="1"/>
+    <col min="14" max="14" width="6.42578125" customWidth="1"/>
+    <col min="15" max="15" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="17"/>
-      <c r="C1" s="16" t="s">
+    <row r="1" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-    </row>
-    <row r="2" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="19" t="s">
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+    </row>
+    <row r="3" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="9" t="s">
+      <c r="O3" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B4" s="20" t="s">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1387,12 +2784,12 @@
       <c r="N4" s="6">
         <v>8</v>
       </c>
-      <c r="O4" s="10">
+      <c r="O4" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="21"/>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B5" s="9"/>
       <c r="C5" s="3" t="s">
         <v>44</v>
       </c>
@@ -1427,12 +2824,12 @@
       <c r="N5" s="5">
         <v>3</v>
       </c>
-      <c r="O5" s="11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="20"/>
+      <c r="O5" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B6" s="8"/>
       <c r="C6" s="1" t="s">
         <v>39</v>
       </c>
@@ -1469,12 +2866,12 @@
       <c r="N6" s="6">
         <v>4</v>
       </c>
-      <c r="O6" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B7" s="21"/>
+      <c r="O6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B7" s="9"/>
       <c r="C7" s="3" t="s">
         <v>49</v>
       </c>
@@ -1495,12 +2892,12 @@
         <v>1</v>
       </c>
       <c r="N7" s="5"/>
-      <c r="O7" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B8" s="20"/>
+      <c r="O7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B8" s="8"/>
       <c r="C8" s="1" t="s">
         <v>10</v>
       </c>
@@ -1517,10 +2914,10 @@
       <c r="L8" s="6"/>
       <c r="M8" s="2"/>
       <c r="N8" s="6"/>
-      <c r="O8" s="10"/>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B9" s="21"/>
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B9" s="9"/>
       <c r="C9" s="3" t="s">
         <v>41</v>
       </c>
@@ -1557,12 +2954,12 @@
       <c r="N9" s="5">
         <v>1</v>
       </c>
-      <c r="O9" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B10" s="20"/>
+      <c r="O9" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B10" s="8"/>
       <c r="C10" s="1" t="s">
         <v>46</v>
       </c>
@@ -1579,10 +2976,10 @@
       <c r="L10" s="6"/>
       <c r="M10" s="2"/>
       <c r="N10" s="6"/>
-      <c r="O10" s="10"/>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B11" s="21"/>
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B11" s="9"/>
       <c r="C11" s="3" t="s">
         <v>40</v>
       </c>
@@ -1619,12 +3016,12 @@
       <c r="N11" s="5">
         <v>6</v>
       </c>
-      <c r="O11" s="11">
+      <c r="O11" s="4">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B12" s="20"/>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B12" s="8"/>
       <c r="C12" s="1" t="s">
         <v>5</v>
       </c>
@@ -1659,12 +3056,12 @@
       <c r="N12" s="6">
         <v>5</v>
       </c>
-      <c r="O12" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B13" s="21"/>
+      <c r="O12" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B13" s="9"/>
       <c r="C13" s="3" t="s">
         <v>0</v>
       </c>
@@ -1701,12 +3098,12 @@
       <c r="N13" s="5">
         <v>22</v>
       </c>
-      <c r="O13" s="11">
+      <c r="O13" s="4">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B14" s="20"/>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B14" s="8"/>
       <c r="C14" s="1" t="s">
         <v>42</v>
       </c>
@@ -1743,12 +3140,12 @@
       <c r="N14" s="6">
         <v>4</v>
       </c>
-      <c r="O14" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B15" s="21"/>
+      <c r="O14" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B15" s="9"/>
       <c r="C15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1767,12 +3164,12 @@
       <c r="N15" s="5">
         <v>1</v>
       </c>
-      <c r="O15" s="11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B16" s="20"/>
+      <c r="O15" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B16" s="8"/>
       <c r="C16" s="1" t="s">
         <v>13</v>
       </c>
@@ -1793,10 +3190,10 @@
         <v>1</v>
       </c>
       <c r="N16" s="6"/>
-      <c r="O16" s="10"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B17" s="21"/>
+      <c r="O16" s="2"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B17" s="9"/>
       <c r="C17" s="3" t="s">
         <v>9</v>
       </c>
@@ -1821,10 +3218,10 @@
       <c r="N17" s="5">
         <v>1</v>
       </c>
-      <c r="O17" s="11"/>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B18" s="20"/>
+      <c r="O17" s="4"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B18" s="8"/>
       <c r="C18" s="1" t="s">
         <v>4</v>
       </c>
@@ -1841,10 +3238,10 @@
       <c r="L18" s="6"/>
       <c r="M18" s="2"/>
       <c r="N18" s="6"/>
-      <c r="O18" s="10"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B19" s="21"/>
+      <c r="O18" s="2"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B19" s="9"/>
       <c r="C19" s="3" t="s">
         <v>14</v>
       </c>
@@ -1865,10 +3262,10 @@
         <v>1</v>
       </c>
       <c r="N19" s="5"/>
-      <c r="O19" s="11"/>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B20" s="20"/>
+      <c r="O19" s="4"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B20" s="8"/>
       <c r="C20" s="1" t="s">
         <v>19</v>
       </c>
@@ -1887,10 +3284,10 @@
         <v>1</v>
       </c>
       <c r="N20" s="6"/>
-      <c r="O20" s="10"/>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B21" s="21"/>
+      <c r="O20" s="2"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B21" s="9"/>
       <c r="C21" s="3" t="s">
         <v>11</v>
       </c>
@@ -1909,10 +3306,10 @@
         <v>1</v>
       </c>
       <c r="N21" s="5"/>
-      <c r="O21" s="11"/>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B22" s="20"/>
+      <c r="O21" s="4"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B22" s="8"/>
       <c r="C22" s="1" t="s">
         <v>8</v>
       </c>
@@ -1931,10 +3328,10 @@
       <c r="L22" s="6"/>
       <c r="M22" s="2"/>
       <c r="N22" s="6"/>
-      <c r="O22" s="10"/>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B23" s="21"/>
+      <c r="O22" s="2"/>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B23" s="9"/>
       <c r="C23" s="3" t="s">
         <v>20</v>
       </c>
@@ -1971,12 +3368,12 @@
       <c r="N23" s="5">
         <v>10</v>
       </c>
-      <c r="O23" s="11">
+      <c r="O23" s="4">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B24" s="20"/>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B24" s="8"/>
       <c r="C24" s="1" t="s">
         <v>50</v>
       </c>
@@ -2003,12 +3400,12 @@
         <v>1</v>
       </c>
       <c r="N24" s="6"/>
-      <c r="O24" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B25" s="21"/>
+      <c r="O24" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B25" s="9"/>
       <c r="C25" s="3" t="s">
         <v>3</v>
       </c>
@@ -2029,12 +3426,12 @@
       <c r="N25" s="5">
         <v>2</v>
       </c>
-      <c r="O25" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B26" s="20"/>
+      <c r="O25" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B26" s="8"/>
       <c r="C26" s="1" t="s">
         <v>18</v>
       </c>
@@ -2071,12 +3468,12 @@
       <c r="N26" s="6">
         <v>3</v>
       </c>
-      <c r="O26" s="10">
+      <c r="O26" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B27" s="21"/>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B27" s="9"/>
       <c r="C27" s="3" t="s">
         <v>45</v>
       </c>
@@ -2113,12 +3510,12 @@
       <c r="N27" s="5">
         <v>10</v>
       </c>
-      <c r="O27" s="11">
+      <c r="O27" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B28" s="20"/>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B28" s="8"/>
       <c r="C28" s="1" t="s">
         <v>12</v>
       </c>
@@ -2141,12 +3538,12 @@
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="6"/>
-      <c r="O28" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B29" s="21"/>
+      <c r="O28" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B29" s="9"/>
       <c r="C29" s="3" t="s">
         <v>2</v>
       </c>
@@ -2183,12 +3580,12 @@
       <c r="N29" s="5">
         <v>4</v>
       </c>
-      <c r="O29" s="11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B30" s="20"/>
+      <c r="O29" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B30" s="8"/>
       <c r="C30" s="1" t="s">
         <v>38</v>
       </c>
@@ -2225,12 +3622,12 @@
       <c r="N30" s="6">
         <v>78</v>
       </c>
-      <c r="O30" s="10">
+      <c r="O30" s="2">
         <v>72</v>
       </c>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B31" s="21"/>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B31" s="9"/>
       <c r="C31" s="3" t="s">
         <v>7</v>
       </c>
@@ -2249,10 +3646,10 @@
         <v>1</v>
       </c>
       <c r="N31" s="5"/>
-      <c r="O31" s="11"/>
-    </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B32" s="20"/>
+      <c r="O31" s="4"/>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B32" s="8"/>
       <c r="C32" s="1" t="s">
         <v>47</v>
       </c>
@@ -2275,12 +3672,12 @@
         <v>1</v>
       </c>
       <c r="N32" s="6"/>
-      <c r="O32" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B33" s="21"/>
+      <c r="O32" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B33" s="9"/>
       <c r="C33" s="3" t="s">
         <v>6</v>
       </c>
@@ -2307,87 +3704,86 @@
       <c r="N33" s="5">
         <v>2</v>
       </c>
-      <c r="O33" s="11"/>
-    </row>
-    <row r="34" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="22"/>
-      <c r="C34" s="12" t="s">
+      <c r="O33" s="4"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B34" s="13"/>
+      <c r="C34" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="13"/>
-      <c r="E34" s="14">
-        <v>1</v>
-      </c>
-      <c r="F34" s="13">
-        <v>1</v>
-      </c>
-      <c r="G34" s="14">
-        <v>2</v>
-      </c>
-      <c r="H34" s="13"/>
-      <c r="I34" s="14">
-        <v>1</v>
-      </c>
-      <c r="J34" s="13"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="13"/>
-      <c r="M34" s="14">
-        <v>1</v>
-      </c>
-      <c r="N34" s="13">
-        <v>1</v>
-      </c>
-      <c r="O34" s="15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="37" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="19" t="s">
+      <c r="D34" s="15"/>
+      <c r="E34" s="16">
+        <v>1</v>
+      </c>
+      <c r="F34" s="15">
+        <v>1</v>
+      </c>
+      <c r="G34" s="16">
+        <v>2</v>
+      </c>
+      <c r="H34" s="15"/>
+      <c r="I34" s="16">
+        <v>1</v>
+      </c>
+      <c r="J34" s="15"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="16">
+        <v>1</v>
+      </c>
+      <c r="N34" s="15">
+        <v>1</v>
+      </c>
+      <c r="O34" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E37" s="8" t="s">
+      <c r="E37" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F37" s="8" t="s">
+      <c r="F37" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G37" s="8" t="s">
+      <c r="G37" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H37" s="8" t="s">
+      <c r="H37" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="I37" s="8" t="s">
+      <c r="I37" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="J37" s="8" t="s">
+      <c r="J37" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K37" s="8" t="s">
+      <c r="K37" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L37" s="8" t="s">
+      <c r="L37" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M37" s="8" t="s">
+      <c r="M37" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="N37" s="8" t="s">
+      <c r="N37" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="O37" s="9" t="s">
+      <c r="O37" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B38" s="21" t="s">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B38" s="9" t="s">
         <v>34</v>
       </c>
       <c r="C38" s="3" t="s">
@@ -2426,12 +3822,12 @@
       <c r="N38" s="5">
         <v>6</v>
       </c>
-      <c r="O38" s="11">
+      <c r="O38" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B39" s="20"/>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B39" s="8"/>
       <c r="C39" s="1" t="s">
         <v>44</v>
       </c>
@@ -2468,12 +3864,12 @@
       <c r="N39" s="6">
         <v>2</v>
       </c>
-      <c r="O39" s="10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B40" s="21"/>
+      <c r="O39" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B40" s="9"/>
       <c r="C40" s="3" t="s">
         <v>39</v>
       </c>
@@ -2510,12 +3906,12 @@
       <c r="N40" s="5">
         <v>14</v>
       </c>
-      <c r="O40" s="11">
+      <c r="O40" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B41" s="20"/>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B41" s="8"/>
       <c r="C41" s="1" t="s">
         <v>49</v>
       </c>
@@ -2532,10 +3928,10 @@
       </c>
       <c r="M41" s="2"/>
       <c r="N41" s="6"/>
-      <c r="O41" s="10"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B42" s="21"/>
+      <c r="O41" s="2"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B42" s="9"/>
       <c r="C42" s="3" t="s">
         <v>10</v>
       </c>
@@ -2554,10 +3950,10 @@
       </c>
       <c r="M42" s="4"/>
       <c r="N42" s="5"/>
-      <c r="O42" s="11"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B43" s="20"/>
+      <c r="O42" s="4"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B43" s="8"/>
       <c r="C43" s="1" t="s">
         <v>41</v>
       </c>
@@ -2592,10 +3988,10 @@
         <v>4</v>
       </c>
       <c r="N43" s="6"/>
-      <c r="O43" s="10"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B44" s="21"/>
+      <c r="O43" s="2"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B44" s="9"/>
       <c r="C44" s="3" t="s">
         <v>46</v>
       </c>
@@ -2614,12 +4010,12 @@
       <c r="L44" s="5"/>
       <c r="M44" s="4"/>
       <c r="N44" s="5"/>
-      <c r="O44" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B45" s="20"/>
+      <c r="O44" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B45" s="8"/>
       <c r="C45" s="1" t="s">
         <v>40</v>
       </c>
@@ -2656,12 +4052,12 @@
       <c r="N45" s="6">
         <v>11</v>
       </c>
-      <c r="O45" s="10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B46" s="21"/>
+      <c r="O45" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B46" s="9"/>
       <c r="C46" s="3" t="s">
         <v>5</v>
       </c>
@@ -2698,10 +4094,10 @@
       <c r="N46" s="5">
         <v>3</v>
       </c>
-      <c r="O46" s="11"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B47" s="20"/>
+      <c r="O46" s="4"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B47" s="8"/>
       <c r="C47" s="1" t="s">
         <v>0</v>
       </c>
@@ -2738,12 +4134,12 @@
       <c r="N47" s="6">
         <v>34</v>
       </c>
-      <c r="O47" s="10">
+      <c r="O47" s="2">
         <v>37</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B48" s="21"/>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B48" s="9"/>
       <c r="C48" s="3" t="s">
         <v>42</v>
       </c>
@@ -2780,12 +4176,12 @@
       <c r="N48" s="5">
         <v>2</v>
       </c>
-      <c r="O48" s="11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B49" s="20"/>
+      <c r="O48" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B49" s="8"/>
       <c r="C49" s="1" t="s">
         <v>1</v>
       </c>
@@ -2804,10 +4200,10 @@
         <v>1</v>
       </c>
       <c r="N49" s="6"/>
-      <c r="O49" s="10"/>
-    </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B50" s="21"/>
+      <c r="O49" s="2"/>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B50" s="9"/>
       <c r="C50" s="3" t="s">
         <v>13</v>
       </c>
@@ -2826,12 +4222,12 @@
       <c r="L50" s="5"/>
       <c r="M50" s="4"/>
       <c r="N50" s="5"/>
-      <c r="O50" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B51" s="20"/>
+      <c r="O50" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B51" s="8"/>
       <c r="C51" s="1" t="s">
         <v>9</v>
       </c>
@@ -2860,12 +4256,12 @@
       <c r="N51" s="6">
         <v>2</v>
       </c>
-      <c r="O51" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B52" s="21"/>
+      <c r="O51" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B52" s="9"/>
       <c r="C52" s="3" t="s">
         <v>14</v>
       </c>
@@ -2892,12 +4288,12 @@
       <c r="N52" s="5">
         <v>1</v>
       </c>
-      <c r="O52" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B53" s="20"/>
+      <c r="O52" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B53" s="8"/>
       <c r="C53" s="1" t="s">
         <v>11</v>
       </c>
@@ -2914,10 +4310,10 @@
       <c r="L53" s="6"/>
       <c r="M53" s="2"/>
       <c r="N53" s="6"/>
-      <c r="O53" s="10"/>
-    </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B54" s="21"/>
+      <c r="O53" s="2"/>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B54" s="9"/>
       <c r="C54" s="3" t="s">
         <v>8</v>
       </c>
@@ -2938,10 +4334,10 @@
         <v>1</v>
       </c>
       <c r="N54" s="5"/>
-      <c r="O54" s="11"/>
-    </row>
-    <row r="55" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B55" s="20"/>
+      <c r="O54" s="4"/>
+    </row>
+    <row r="55" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B55" s="8"/>
       <c r="C55" s="1" t="s">
         <v>20</v>
       </c>
@@ -2978,12 +4374,12 @@
       <c r="N55" s="6">
         <v>20</v>
       </c>
-      <c r="O55" s="10">
+      <c r="O55" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B56" s="21"/>
+    <row r="56" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B56" s="9"/>
       <c r="C56" s="3" t="s">
         <v>50</v>
       </c>
@@ -3004,10 +4400,10 @@
       <c r="L56" s="5"/>
       <c r="M56" s="4"/>
       <c r="N56" s="5"/>
-      <c r="O56" s="11"/>
-    </row>
-    <row r="57" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B57" s="20"/>
+      <c r="O56" s="4"/>
+    </row>
+    <row r="57" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B57" s="8"/>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
@@ -3030,12 +4426,12 @@
         <v>2</v>
       </c>
       <c r="N57" s="6"/>
-      <c r="O57" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B58" s="21"/>
+      <c r="O57" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B58" s="9"/>
       <c r="C58" s="3" t="s">
         <v>18</v>
       </c>
@@ -3072,12 +4468,12 @@
       <c r="N58" s="5">
         <v>6</v>
       </c>
-      <c r="O58" s="11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B59" s="20"/>
+      <c r="O58" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B59" s="8"/>
       <c r="C59" s="1" t="s">
         <v>45</v>
       </c>
@@ -3114,12 +4510,12 @@
       <c r="N59" s="6">
         <v>6</v>
       </c>
-      <c r="O59" s="10">
+      <c r="O59" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B60" s="21"/>
+    <row r="60" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B60" s="9"/>
       <c r="C60" s="3" t="s">
         <v>12</v>
       </c>
@@ -3142,12 +4538,12 @@
       <c r="N60" s="5">
         <v>1</v>
       </c>
-      <c r="O60" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B61" s="20"/>
+      <c r="O60" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B61" s="8"/>
       <c r="C61" s="1" t="s">
         <v>2</v>
       </c>
@@ -3180,12 +4576,12 @@
       <c r="N61" s="6">
         <v>4</v>
       </c>
-      <c r="O61" s="10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B62" s="21"/>
+      <c r="O61" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B62" s="9"/>
       <c r="C62" s="3" t="s">
         <v>38</v>
       </c>
@@ -3222,12 +4618,12 @@
       <c r="N62" s="5">
         <v>79</v>
       </c>
-      <c r="O62" s="11">
+      <c r="O62" s="4">
         <v>76</v>
       </c>
     </row>
-    <row r="63" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B63" s="20"/>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B63" s="8"/>
       <c r="C63" s="1" t="s">
         <v>7</v>
       </c>
@@ -3250,10 +4646,10 @@
       </c>
       <c r="M63" s="2"/>
       <c r="N63" s="6"/>
-      <c r="O63" s="10"/>
-    </row>
-    <row r="64" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B64" s="21"/>
+      <c r="O63" s="2"/>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B64" s="9"/>
       <c r="C64" s="3" t="s">
         <v>47</v>
       </c>
@@ -3284,12 +4680,12 @@
       <c r="N64" s="5">
         <v>1</v>
       </c>
-      <c r="O64" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B65" s="20"/>
+      <c r="O64" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B65" s="8"/>
       <c r="C65" s="1" t="s">
         <v>6</v>
       </c>
@@ -3314,79 +4710,78 @@
       </c>
       <c r="M65" s="2"/>
       <c r="N65" s="6"/>
-      <c r="O65" s="10"/>
-    </row>
-    <row r="66" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="22"/>
-      <c r="C66" s="12" t="s">
+      <c r="O65" s="2"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B66" s="13"/>
+      <c r="C66" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D66" s="13">
-        <v>2</v>
-      </c>
-      <c r="E66" s="14">
-        <v>1</v>
-      </c>
-      <c r="F66" s="13"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="14"/>
-      <c r="J66" s="13"/>
-      <c r="K66" s="14"/>
-      <c r="L66" s="13"/>
-      <c r="M66" s="14"/>
-      <c r="N66" s="13"/>
-      <c r="O66" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="69" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="19" t="s">
+      <c r="D66" s="15">
+        <v>2</v>
+      </c>
+      <c r="E66" s="16">
+        <v>1</v>
+      </c>
+      <c r="F66" s="15"/>
+      <c r="G66" s="16"/>
+      <c r="H66" s="15"/>
+      <c r="I66" s="16"/>
+      <c r="J66" s="15"/>
+      <c r="K66" s="16"/>
+      <c r="L66" s="15"/>
+      <c r="M66" s="16"/>
+      <c r="N66" s="15"/>
+      <c r="O66" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="C69" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="D69" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="E69" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F69" s="8" t="s">
+      <c r="F69" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G69" s="8" t="s">
+      <c r="G69" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H69" s="8" t="s">
+      <c r="H69" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="I69" s="8" t="s">
+      <c r="I69" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="J69" s="8" t="s">
+      <c r="J69" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K69" s="8" t="s">
+      <c r="K69" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L69" s="8" t="s">
+      <c r="L69" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M69" s="8" t="s">
+      <c r="M69" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="N69" s="8" t="s">
+      <c r="N69" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="O69" s="9" t="s">
+      <c r="O69" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B70" s="20" t="s">
+    <row r="70" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B70" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C70" s="1" t="s">
@@ -3425,12 +4820,12 @@
       <c r="N70" s="6">
         <v>15</v>
       </c>
-      <c r="O70" s="10">
+      <c r="O70" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B71" s="21"/>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B71" s="9"/>
       <c r="C71" s="3" t="s">
         <v>44</v>
       </c>
@@ -3467,12 +4862,12 @@
       <c r="N71" s="5">
         <v>7</v>
       </c>
-      <c r="O71" s="11">
+      <c r="O71" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B72" s="20"/>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B72" s="8"/>
       <c r="C72" s="1" t="s">
         <v>39</v>
       </c>
@@ -3509,12 +4904,12 @@
       <c r="N72" s="6">
         <v>13</v>
       </c>
-      <c r="O72" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B73" s="21"/>
+      <c r="O72" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B73" s="9"/>
       <c r="C73" s="3" t="s">
         <v>49</v>
       </c>
@@ -3529,12 +4924,12 @@
       <c r="L73" s="5"/>
       <c r="M73" s="4"/>
       <c r="N73" s="5"/>
-      <c r="O73" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B74" s="20"/>
+      <c r="O73" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B74" s="8"/>
       <c r="C74" s="1" t="s">
         <v>10</v>
       </c>
@@ -3555,12 +4950,12 @@
         <v>2</v>
       </c>
       <c r="N74" s="6"/>
-      <c r="O74" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B75" s="21"/>
+      <c r="O74" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B75" s="9"/>
       <c r="C75" s="3" t="s">
         <v>41</v>
       </c>
@@ -3593,12 +4988,12 @@
       <c r="N75" s="5">
         <v>2</v>
       </c>
-      <c r="O75" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B76" s="20"/>
+      <c r="O75" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B76" s="8"/>
       <c r="C76" s="1" t="s">
         <v>46</v>
       </c>
@@ -3619,10 +5014,10 @@
       <c r="N76" s="6">
         <v>2</v>
       </c>
-      <c r="O76" s="10"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B77" s="21"/>
+      <c r="O76" s="2"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B77" s="9"/>
       <c r="C77" s="3" t="s">
         <v>40</v>
       </c>
@@ -3659,12 +5054,12 @@
       <c r="N77" s="5">
         <v>10</v>
       </c>
-      <c r="O77" s="11">
+      <c r="O77" s="4">
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B78" s="20"/>
+    <row r="78" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B78" s="8"/>
       <c r="C78" s="1" t="s">
         <v>5</v>
       </c>
@@ -3699,12 +5094,12 @@
       <c r="N78" s="6">
         <v>3</v>
       </c>
-      <c r="O78" s="10">
+      <c r="O78" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B79" s="21"/>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B79" s="9"/>
       <c r="C79" s="3" t="s">
         <v>0</v>
       </c>
@@ -3741,12 +5136,12 @@
       <c r="N79" s="5">
         <v>42</v>
       </c>
-      <c r="O79" s="11">
+      <c r="O79" s="4">
         <v>40</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B80" s="20"/>
+    <row r="80" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B80" s="8"/>
       <c r="C80" s="1" t="s">
         <v>42</v>
       </c>
@@ -3781,12 +5176,12 @@
       <c r="N80" s="6">
         <v>4</v>
       </c>
-      <c r="O80" s="10">
+      <c r="O80" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B81" s="21"/>
+    <row r="81" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B81" s="9"/>
       <c r="C81" s="3" t="s">
         <v>1</v>
       </c>
@@ -3811,10 +5206,10 @@
       <c r="N81" s="5">
         <v>1</v>
       </c>
-      <c r="O81" s="11"/>
-    </row>
-    <row r="82" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B82" s="20"/>
+      <c r="O81" s="4"/>
+    </row>
+    <row r="82" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B82" s="8"/>
       <c r="C82" s="1" t="s">
         <v>16</v>
       </c>
@@ -3833,10 +5228,10 @@
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="6"/>
-      <c r="O82" s="10"/>
-    </row>
-    <row r="83" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B83" s="21"/>
+      <c r="O82" s="2"/>
+    </row>
+    <row r="83" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B83" s="9"/>
       <c r="C83" s="3" t="s">
         <v>13</v>
       </c>
@@ -3855,10 +5250,10 @@
       <c r="L83" s="5"/>
       <c r="M83" s="4"/>
       <c r="N83" s="5"/>
-      <c r="O83" s="11"/>
-    </row>
-    <row r="84" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B84" s="20"/>
+      <c r="O83" s="4"/>
+    </row>
+    <row r="84" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B84" s="8"/>
       <c r="C84" s="1" t="s">
         <v>9</v>
       </c>
@@ -3885,10 +5280,10 @@
         <v>3</v>
       </c>
       <c r="N84" s="6"/>
-      <c r="O84" s="10"/>
-    </row>
-    <row r="85" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B85" s="21"/>
+      <c r="O84" s="2"/>
+    </row>
+    <row r="85" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B85" s="9"/>
       <c r="C85" s="3" t="s">
         <v>4</v>
       </c>
@@ -3905,10 +5300,10 @@
       <c r="L85" s="5"/>
       <c r="M85" s="4"/>
       <c r="N85" s="5"/>
-      <c r="O85" s="11"/>
-    </row>
-    <row r="86" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B86" s="20"/>
+      <c r="O85" s="4"/>
+    </row>
+    <row r="86" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B86" s="8"/>
       <c r="C86" s="1" t="s">
         <v>14</v>
       </c>
@@ -3933,12 +5328,12 @@
       <c r="L86" s="6"/>
       <c r="M86" s="2"/>
       <c r="N86" s="6"/>
-      <c r="O86" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B87" s="21"/>
+      <c r="O86" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B87" s="9"/>
       <c r="C87" s="3" t="s">
         <v>19</v>
       </c>
@@ -3955,10 +5350,10 @@
       <c r="L87" s="5"/>
       <c r="M87" s="4"/>
       <c r="N87" s="5"/>
-      <c r="O87" s="11"/>
-    </row>
-    <row r="88" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B88" s="20"/>
+      <c r="O87" s="4"/>
+    </row>
+    <row r="88" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B88" s="8"/>
       <c r="C88" s="1" t="s">
         <v>11</v>
       </c>
@@ -3977,10 +5372,10 @@
       </c>
       <c r="M88" s="2"/>
       <c r="N88" s="6"/>
-      <c r="O88" s="10"/>
-    </row>
-    <row r="89" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B89" s="21"/>
+      <c r="O88" s="2"/>
+    </row>
+    <row r="89" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B89" s="9"/>
       <c r="C89" s="3" t="s">
         <v>51</v>
       </c>
@@ -4001,12 +5396,12 @@
       <c r="N89" s="5">
         <v>1</v>
       </c>
-      <c r="O89" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B90" s="20"/>
+      <c r="O89" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B90" s="8"/>
       <c r="C90" s="1" t="s">
         <v>8</v>
       </c>
@@ -4029,10 +5424,10 @@
       <c r="N90" s="6">
         <v>2</v>
       </c>
-      <c r="O90" s="10"/>
-    </row>
-    <row r="91" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B91" s="21"/>
+      <c r="O90" s="2"/>
+    </row>
+    <row r="91" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B91" s="9"/>
       <c r="C91" s="3" t="s">
         <v>20</v>
       </c>
@@ -4069,12 +5464,12 @@
       <c r="N91" s="5">
         <v>23</v>
       </c>
-      <c r="O91" s="11">
+      <c r="O91" s="4">
         <v>22</v>
       </c>
     </row>
-    <row r="92" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B92" s="20"/>
+    <row r="92" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B92" s="8"/>
       <c r="C92" s="1" t="s">
         <v>50</v>
       </c>
@@ -4099,10 +5494,10 @@
         <v>1</v>
       </c>
       <c r="N92" s="6"/>
-      <c r="O92" s="10"/>
-    </row>
-    <row r="93" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B93" s="21"/>
+      <c r="O92" s="2"/>
+    </row>
+    <row r="93" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B93" s="9"/>
       <c r="C93" s="3" t="s">
         <v>3</v>
       </c>
@@ -4127,12 +5522,12 @@
         <v>2</v>
       </c>
       <c r="N93" s="5"/>
-      <c r="O93" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B94" s="20"/>
+      <c r="O93" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B94" s="8"/>
       <c r="C94" s="1" t="s">
         <v>18</v>
       </c>
@@ -4169,12 +5564,12 @@
       <c r="N94" s="6">
         <v>7</v>
       </c>
-      <c r="O94" s="10">
+      <c r="O94" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B95" s="21"/>
+    <row r="95" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B95" s="9"/>
       <c r="C95" s="3" t="s">
         <v>45</v>
       </c>
@@ -4211,12 +5606,12 @@
       <c r="N95" s="5">
         <v>7</v>
       </c>
-      <c r="O95" s="11">
+      <c r="O95" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B96" s="20"/>
+    <row r="96" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B96" s="8"/>
       <c r="C96" s="1" t="s">
         <v>12</v>
       </c>
@@ -4245,12 +5640,12 @@
         <v>3</v>
       </c>
       <c r="N96" s="6"/>
-      <c r="O96" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B97" s="21"/>
+      <c r="O96" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B97" s="9"/>
       <c r="C97" s="3" t="s">
         <v>2</v>
       </c>
@@ -4283,12 +5678,12 @@
         <v>6</v>
       </c>
       <c r="N97" s="5"/>
-      <c r="O97" s="11">
+      <c r="O97" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B98" s="20"/>
+    <row r="98" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B98" s="8"/>
       <c r="C98" s="1" t="s">
         <v>15</v>
       </c>
@@ -4309,12 +5704,12 @@
       <c r="N98" s="6">
         <v>3</v>
       </c>
-      <c r="O98" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B99" s="21"/>
+      <c r="O98" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B99" s="9"/>
       <c r="C99" s="3" t="s">
         <v>38</v>
       </c>
@@ -4351,12 +5746,12 @@
       <c r="N99" s="5">
         <v>97</v>
       </c>
-      <c r="O99" s="11">
+      <c r="O99" s="4">
         <v>135</v>
       </c>
     </row>
-    <row r="100" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B100" s="20"/>
+    <row r="100" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B100" s="8"/>
       <c r="C100" s="1" t="s">
         <v>7</v>
       </c>
@@ -4387,10 +5782,10 @@
         <v>1</v>
       </c>
       <c r="N100" s="6"/>
-      <c r="O100" s="10"/>
-    </row>
-    <row r="101" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B101" s="21"/>
+      <c r="O100" s="2"/>
+    </row>
+    <row r="101" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B101" s="9"/>
       <c r="C101" s="3" t="s">
         <v>47</v>
       </c>
@@ -4425,12 +5820,12 @@
       <c r="N101" s="5">
         <v>2</v>
       </c>
-      <c r="O101" s="11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B102" s="20"/>
+      <c r="O101" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B102" s="8"/>
       <c r="C102" s="1" t="s">
         <v>6</v>
       </c>
@@ -4459,93 +5854,92 @@
         <v>1</v>
       </c>
       <c r="N102" s="6"/>
-      <c r="O102" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="103" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="22"/>
-      <c r="C103" s="12" t="s">
+      <c r="O102" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B103" s="13"/>
+      <c r="C103" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D103" s="13"/>
-      <c r="E103" s="14">
-        <v>1</v>
-      </c>
-      <c r="F103" s="13">
-        <v>1</v>
-      </c>
-      <c r="G103" s="14">
-        <v>1</v>
-      </c>
-      <c r="H103" s="13">
-        <v>1</v>
-      </c>
-      <c r="I103" s="14">
-        <v>3</v>
-      </c>
-      <c r="J103" s="13">
-        <v>1</v>
-      </c>
-      <c r="K103" s="14"/>
-      <c r="L103" s="13">
-        <v>4</v>
-      </c>
-      <c r="M103" s="14">
-        <v>1</v>
-      </c>
-      <c r="N103" s="13">
-        <v>2</v>
-      </c>
-      <c r="O103" s="15"/>
-    </row>
-    <row r="105" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="106" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B106" s="19" t="s">
+      <c r="D103" s="15"/>
+      <c r="E103" s="16">
+        <v>1</v>
+      </c>
+      <c r="F103" s="15">
+        <v>1</v>
+      </c>
+      <c r="G103" s="16">
+        <v>1</v>
+      </c>
+      <c r="H103" s="15">
+        <v>1</v>
+      </c>
+      <c r="I103" s="16">
+        <v>3</v>
+      </c>
+      <c r="J103" s="15">
+        <v>1</v>
+      </c>
+      <c r="K103" s="16"/>
+      <c r="L103" s="15">
+        <v>4</v>
+      </c>
+      <c r="M103" s="16">
+        <v>1</v>
+      </c>
+      <c r="N103" s="15">
+        <v>2</v>
+      </c>
+      <c r="O103" s="16"/>
+    </row>
+    <row r="106" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B106" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C106" s="7" t="s">
+      <c r="C106" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D106" s="8" t="s">
+      <c r="D106" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E106" s="8" t="s">
+      <c r="E106" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F106" s="8" t="s">
+      <c r="F106" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G106" s="8" t="s">
+      <c r="G106" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H106" s="8" t="s">
+      <c r="H106" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="I106" s="8" t="s">
+      <c r="I106" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="J106" s="8" t="s">
+      <c r="J106" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K106" s="8" t="s">
+      <c r="K106" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L106" s="8" t="s">
+      <c r="L106" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M106" s="8" t="s">
+      <c r="M106" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="N106" s="8" t="s">
+      <c r="N106" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="O106" s="9" t="s">
+      <c r="O106" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="107" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B107" s="20" t="s">
+    <row r="107" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B107" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C107" s="1" t="s">
@@ -4584,12 +5978,12 @@
       <c r="N107" s="6">
         <v>8</v>
       </c>
-      <c r="O107" s="10">
+      <c r="O107" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B108" s="21"/>
+    <row r="108" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B108" s="9"/>
       <c r="C108" s="3" t="s">
         <v>44</v>
       </c>
@@ -4626,12 +6020,12 @@
       <c r="N108" s="5">
         <v>3</v>
       </c>
-      <c r="O108" s="11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="109" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B109" s="20"/>
+      <c r="O108" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B109" s="8"/>
       <c r="C109" s="1" t="s">
         <v>39</v>
       </c>
@@ -4668,12 +6062,12 @@
       <c r="N109" s="6">
         <v>9</v>
       </c>
-      <c r="O109" s="10">
+      <c r="O109" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B110" s="21"/>
+    <row r="110" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B110" s="9"/>
       <c r="C110" s="3" t="s">
         <v>49</v>
       </c>
@@ -4692,10 +6086,10 @@
       <c r="L110" s="5"/>
       <c r="M110" s="4"/>
       <c r="N110" s="5"/>
-      <c r="O110" s="11"/>
-    </row>
-    <row r="111" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B111" s="20"/>
+      <c r="O110" s="4"/>
+    </row>
+    <row r="111" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B111" s="8"/>
       <c r="C111" s="1" t="s">
         <v>10</v>
       </c>
@@ -4714,10 +6108,10 @@
       <c r="L111" s="6"/>
       <c r="M111" s="2"/>
       <c r="N111" s="6"/>
-      <c r="O111" s="10"/>
-    </row>
-    <row r="112" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B112" s="21"/>
+      <c r="O111" s="2"/>
+    </row>
+    <row r="112" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B112" s="9"/>
       <c r="C112" s="3" t="s">
         <v>41</v>
       </c>
@@ -4750,10 +6144,10 @@
       <c r="N112" s="5">
         <v>4</v>
       </c>
-      <c r="O112" s="11"/>
-    </row>
-    <row r="113" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B113" s="20"/>
+      <c r="O112" s="4"/>
+    </row>
+    <row r="113" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B113" s="8"/>
       <c r="C113" s="1" t="s">
         <v>46</v>
       </c>
@@ -4774,10 +6168,10 @@
       <c r="N113" s="6">
         <v>1</v>
       </c>
-      <c r="O113" s="10"/>
-    </row>
-    <row r="114" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B114" s="21"/>
+      <c r="O113" s="2"/>
+    </row>
+    <row r="114" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B114" s="9"/>
       <c r="C114" s="3" t="s">
         <v>40</v>
       </c>
@@ -4814,12 +6208,12 @@
       <c r="N114" s="5">
         <v>4</v>
       </c>
-      <c r="O114" s="11">
+      <c r="O114" s="4">
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B115" s="20"/>
+    <row r="115" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B115" s="8"/>
       <c r="C115" s="1" t="s">
         <v>5</v>
       </c>
@@ -4856,12 +6250,12 @@
       <c r="N115" s="6">
         <v>9</v>
       </c>
-      <c r="O115" s="10">
+      <c r="O115" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B116" s="21"/>
+    <row r="116" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B116" s="9"/>
       <c r="C116" s="3" t="s">
         <v>0</v>
       </c>
@@ -4898,12 +6292,12 @@
       <c r="N116" s="5">
         <v>32</v>
       </c>
-      <c r="O116" s="11">
+      <c r="O116" s="4">
         <v>53</v>
       </c>
     </row>
-    <row r="117" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B117" s="20"/>
+    <row r="117" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B117" s="8"/>
       <c r="C117" s="1" t="s">
         <v>42</v>
       </c>
@@ -4936,10 +6330,10 @@
       <c r="N117" s="6">
         <v>2</v>
       </c>
-      <c r="O117" s="10"/>
-    </row>
-    <row r="118" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B118" s="21"/>
+      <c r="O117" s="2"/>
+    </row>
+    <row r="118" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B118" s="9"/>
       <c r="C118" s="3" t="s">
         <v>1</v>
       </c>
@@ -4968,12 +6362,12 @@
       <c r="N118" s="5">
         <v>1</v>
       </c>
-      <c r="O118" s="11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="119" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B119" s="20"/>
+      <c r="O118" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B119" s="8"/>
       <c r="C119" s="1" t="s">
         <v>16</v>
       </c>
@@ -4996,10 +6390,10 @@
       <c r="L119" s="6"/>
       <c r="M119" s="2"/>
       <c r="N119" s="6"/>
-      <c r="O119" s="10"/>
-    </row>
-    <row r="120" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B120" s="21"/>
+      <c r="O119" s="2"/>
+    </row>
+    <row r="120" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B120" s="9"/>
       <c r="C120" s="3" t="s">
         <v>13</v>
       </c>
@@ -5018,10 +6412,10 @@
       <c r="L120" s="5"/>
       <c r="M120" s="4"/>
       <c r="N120" s="5"/>
-      <c r="O120" s="11"/>
-    </row>
-    <row r="121" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B121" s="20"/>
+      <c r="O120" s="4"/>
+    </row>
+    <row r="121" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B121" s="8"/>
       <c r="C121" s="1" t="s">
         <v>9</v>
       </c>
@@ -5048,12 +6442,12 @@
       </c>
       <c r="M121" s="2"/>
       <c r="N121" s="6"/>
-      <c r="O121" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B122" s="21"/>
+      <c r="O121" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B122" s="9"/>
       <c r="C122" s="3" t="s">
         <v>4</v>
       </c>
@@ -5070,10 +6464,10 @@
       <c r="N122" s="5">
         <v>1</v>
       </c>
-      <c r="O122" s="11"/>
-    </row>
-    <row r="123" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B123" s="20"/>
+      <c r="O122" s="4"/>
+    </row>
+    <row r="123" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B123" s="8"/>
       <c r="C123" s="1" t="s">
         <v>14</v>
       </c>
@@ -5094,10 +6488,10 @@
       <c r="N123" s="6">
         <v>1</v>
       </c>
-      <c r="O123" s="10"/>
-    </row>
-    <row r="124" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B124" s="21"/>
+      <c r="O123" s="2"/>
+    </row>
+    <row r="124" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B124" s="9"/>
       <c r="C124" s="3" t="s">
         <v>11</v>
       </c>
@@ -5114,10 +6508,10 @@
       <c r="L124" s="5"/>
       <c r="M124" s="4"/>
       <c r="N124" s="5"/>
-      <c r="O124" s="11"/>
-    </row>
-    <row r="125" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B125" s="20"/>
+      <c r="O124" s="4"/>
+    </row>
+    <row r="125" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B125" s="8"/>
       <c r="C125" s="1" t="s">
         <v>51</v>
       </c>
@@ -5134,10 +6528,10 @@
       <c r="L125" s="6"/>
       <c r="M125" s="2"/>
       <c r="N125" s="6"/>
-      <c r="O125" s="10"/>
-    </row>
-    <row r="126" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B126" s="21"/>
+      <c r="O125" s="2"/>
+    </row>
+    <row r="126" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B126" s="9"/>
       <c r="C126" s="3" t="s">
         <v>8</v>
       </c>
@@ -5162,12 +6556,12 @@
         <v>1</v>
       </c>
       <c r="N126" s="5"/>
-      <c r="O126" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B127" s="20"/>
+      <c r="O126" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B127" s="8"/>
       <c r="C127" s="1" t="s">
         <v>20</v>
       </c>
@@ -5204,12 +6598,12 @@
       <c r="N127" s="6">
         <v>23</v>
       </c>
-      <c r="O127" s="10">
+      <c r="O127" s="2">
         <v>14</v>
       </c>
     </row>
-    <row r="128" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B128" s="21"/>
+    <row r="128" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B128" s="9"/>
       <c r="C128" s="3" t="s">
         <v>50</v>
       </c>
@@ -5238,12 +6632,12 @@
       <c r="N128" s="5">
         <v>1</v>
       </c>
-      <c r="O128" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B129" s="20"/>
+      <c r="O128" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B129" s="8"/>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
@@ -5266,12 +6660,12 @@
       <c r="N129" s="6">
         <v>1</v>
       </c>
-      <c r="O129" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="130" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B130" s="21"/>
+      <c r="O129" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B130" s="9"/>
       <c r="C130" s="3" t="s">
         <v>18</v>
       </c>
@@ -5308,12 +6702,12 @@
       <c r="N130" s="5">
         <v>1</v>
       </c>
-      <c r="O130" s="11">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="131" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B131" s="20"/>
+      <c r="O130" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B131" s="8"/>
       <c r="C131" s="1" t="s">
         <v>17</v>
       </c>
@@ -5330,10 +6724,10 @@
       <c r="L131" s="6"/>
       <c r="M131" s="2"/>
       <c r="N131" s="6"/>
-      <c r="O131" s="10"/>
-    </row>
-    <row r="132" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B132" s="21"/>
+      <c r="O131" s="2"/>
+    </row>
+    <row r="132" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B132" s="9"/>
       <c r="C132" s="3" t="s">
         <v>45</v>
       </c>
@@ -5370,12 +6764,12 @@
       <c r="N132" s="5">
         <v>14</v>
       </c>
-      <c r="O132" s="11">
+      <c r="O132" s="4">
         <v>21</v>
       </c>
     </row>
-    <row r="133" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B133" s="20"/>
+    <row r="133" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B133" s="8"/>
       <c r="C133" s="1" t="s">
         <v>12</v>
       </c>
@@ -5408,12 +6802,12 @@
       <c r="N133" s="6">
         <v>1</v>
       </c>
-      <c r="O133" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B134" s="21"/>
+      <c r="O133" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B134" s="9"/>
       <c r="C134" s="3" t="s">
         <v>2</v>
       </c>
@@ -5450,12 +6844,12 @@
       <c r="N134" s="5">
         <v>6</v>
       </c>
-      <c r="O134" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="135" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B135" s="20"/>
+      <c r="O134" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="135" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B135" s="8"/>
       <c r="C135" s="1" t="s">
         <v>15</v>
       </c>
@@ -5474,10 +6868,10 @@
         <v>1</v>
       </c>
       <c r="N135" s="6"/>
-      <c r="O135" s="10"/>
-    </row>
-    <row r="136" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B136" s="21"/>
+      <c r="O135" s="2"/>
+    </row>
+    <row r="136" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B136" s="9"/>
       <c r="C136" s="3" t="s">
         <v>38</v>
       </c>
@@ -5514,12 +6908,12 @@
       <c r="N136" s="5">
         <v>77</v>
       </c>
-      <c r="O136" s="11">
+      <c r="O136" s="4">
         <v>73</v>
       </c>
     </row>
-    <row r="137" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B137" s="20"/>
+    <row r="137" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B137" s="8"/>
       <c r="C137" s="1" t="s">
         <v>7</v>
       </c>
@@ -5544,12 +6938,12 @@
         <v>1</v>
       </c>
       <c r="N137" s="6"/>
-      <c r="O137" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B138" s="21"/>
+      <c r="O137" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B138" s="9"/>
       <c r="C138" s="3" t="s">
         <v>47</v>
       </c>
@@ -5582,10 +6976,10 @@
       <c r="N138" s="5">
         <v>2</v>
       </c>
-      <c r="O138" s="11"/>
-    </row>
-    <row r="139" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B139" s="20"/>
+      <c r="O138" s="4"/>
+    </row>
+    <row r="139" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B139" s="8"/>
       <c r="C139" s="1" t="s">
         <v>6</v>
       </c>
@@ -5618,83 +7012,82 @@
       <c r="N139" s="6">
         <v>1</v>
       </c>
-      <c r="O139" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B140" s="22"/>
-      <c r="C140" s="12" t="s">
+      <c r="O139" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B140" s="13"/>
+      <c r="C140" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D140" s="13"/>
-      <c r="E140" s="14"/>
-      <c r="F140" s="13">
-        <v>1</v>
-      </c>
-      <c r="G140" s="14">
-        <v>1</v>
-      </c>
-      <c r="H140" s="13">
-        <v>1</v>
-      </c>
-      <c r="I140" s="14"/>
-      <c r="J140" s="13"/>
-      <c r="K140" s="14"/>
-      <c r="L140" s="13"/>
-      <c r="M140" s="14"/>
-      <c r="N140" s="13"/>
-      <c r="O140" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="143" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B143" s="19" t="s">
+      <c r="D140" s="15"/>
+      <c r="E140" s="16"/>
+      <c r="F140" s="15">
+        <v>1</v>
+      </c>
+      <c r="G140" s="16">
+        <v>1</v>
+      </c>
+      <c r="H140" s="15">
+        <v>1</v>
+      </c>
+      <c r="I140" s="16"/>
+      <c r="J140" s="15"/>
+      <c r="K140" s="16"/>
+      <c r="L140" s="15"/>
+      <c r="M140" s="16"/>
+      <c r="N140" s="15"/>
+      <c r="O140" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B143" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C143" s="7" t="s">
+      <c r="C143" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="D143" s="8" t="s">
+      <c r="D143" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E143" s="8" t="s">
+      <c r="E143" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="F143" s="8" t="s">
+      <c r="F143" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="G143" s="8" t="s">
+      <c r="G143" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H143" s="8" t="s">
+      <c r="H143" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="I143" s="8" t="s">
+      <c r="I143" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="J143" s="8" t="s">
+      <c r="J143" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K143" s="8" t="s">
+      <c r="K143" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="L143" s="8" t="s">
+      <c r="L143" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="M143" s="8" t="s">
+      <c r="M143" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="N143" s="8" t="s">
+      <c r="N143" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="O143" s="9" t="s">
+      <c r="O143" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="144" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B144" s="20" t="s">
+    <row r="144" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B144" s="8" t="s">
         <v>37</v>
       </c>
       <c r="C144" s="1" t="s">
@@ -5733,12 +7126,12 @@
       <c r="N144" s="6">
         <v>15</v>
       </c>
-      <c r="O144" s="10">
+      <c r="O144" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B145" s="21"/>
+    <row r="145" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B145" s="9"/>
       <c r="C145" s="3" t="s">
         <v>44</v>
       </c>
@@ -5775,12 +7168,12 @@
       <c r="N145" s="5">
         <v>1</v>
       </c>
-      <c r="O145" s="11">
+      <c r="O145" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="146" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B146" s="20"/>
+    <row r="146" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B146" s="8"/>
       <c r="C146" s="1" t="s">
         <v>39</v>
       </c>
@@ -5817,12 +7210,12 @@
       <c r="N146" s="6">
         <v>8</v>
       </c>
-      <c r="O146" s="10">
+      <c r="O146" s="2">
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B147" s="21"/>
+    <row r="147" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B147" s="9"/>
       <c r="C147" s="3" t="s">
         <v>49</v>
       </c>
@@ -5847,10 +7240,10 @@
       <c r="N147" s="5">
         <v>1</v>
       </c>
-      <c r="O147" s="11"/>
-    </row>
-    <row r="148" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B148" s="20"/>
+      <c r="O147" s="4"/>
+    </row>
+    <row r="148" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B148" s="8"/>
       <c r="C148" s="1" t="s">
         <v>10</v>
       </c>
@@ -5871,10 +7264,10 @@
         <v>1</v>
       </c>
       <c r="N148" s="6"/>
-      <c r="O148" s="10"/>
-    </row>
-    <row r="149" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B149" s="21"/>
+      <c r="O148" s="2"/>
+    </row>
+    <row r="149" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B149" s="9"/>
       <c r="C149" s="3" t="s">
         <v>41</v>
       </c>
@@ -5907,12 +7300,12 @@
       <c r="N149" s="5">
         <v>4</v>
       </c>
-      <c r="O149" s="11">
+      <c r="O149" s="4">
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B150" s="20"/>
+    <row r="150" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B150" s="8"/>
       <c r="C150" s="1" t="s">
         <v>46</v>
       </c>
@@ -5937,10 +7330,10 @@
         <v>2</v>
       </c>
       <c r="N150" s="6"/>
-      <c r="O150" s="10"/>
-    </row>
-    <row r="151" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B151" s="21"/>
+      <c r="O150" s="2"/>
+    </row>
+    <row r="151" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B151" s="9"/>
       <c r="C151" s="3" t="s">
         <v>40</v>
       </c>
@@ -5977,12 +7370,12 @@
       <c r="N151" s="5">
         <v>15</v>
       </c>
-      <c r="O151" s="11">
+      <c r="O151" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="152" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B152" s="20"/>
+    <row r="152" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B152" s="8"/>
       <c r="C152" s="1" t="s">
         <v>5</v>
       </c>
@@ -6019,12 +7412,12 @@
       <c r="N152" s="6">
         <v>6</v>
       </c>
-      <c r="O152" s="10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="153" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B153" s="21"/>
+      <c r="O152" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B153" s="9"/>
       <c r="C153" s="3" t="s">
         <v>0</v>
       </c>
@@ -6061,12 +7454,12 @@
       <c r="N153" s="5">
         <v>29</v>
       </c>
-      <c r="O153" s="11">
+      <c r="O153" s="4">
         <v>20</v>
       </c>
     </row>
-    <row r="154" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B154" s="20"/>
+    <row r="154" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B154" s="8"/>
       <c r="C154" s="1" t="s">
         <v>42</v>
       </c>
@@ -6097,12 +7490,12 @@
         <v>5</v>
       </c>
       <c r="N154" s="6"/>
-      <c r="O154" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B155" s="21"/>
+      <c r="O154" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B155" s="9"/>
       <c r="C155" s="3" t="s">
         <v>1</v>
       </c>
@@ -6123,10 +7516,10 @@
       <c r="L155" s="5"/>
       <c r="M155" s="4"/>
       <c r="N155" s="5"/>
-      <c r="O155" s="11"/>
-    </row>
-    <row r="156" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B156" s="20"/>
+      <c r="O155" s="4"/>
+    </row>
+    <row r="156" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B156" s="8"/>
       <c r="C156" s="1" t="s">
         <v>16</v>
       </c>
@@ -6147,10 +7540,10 @@
       <c r="L156" s="6"/>
       <c r="M156" s="2"/>
       <c r="N156" s="6"/>
-      <c r="O156" s="10"/>
-    </row>
-    <row r="157" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B157" s="21"/>
+      <c r="O156" s="2"/>
+    </row>
+    <row r="157" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B157" s="9"/>
       <c r="C157" s="3" t="s">
         <v>13</v>
       </c>
@@ -6169,10 +7562,10 @@
         <v>2</v>
       </c>
       <c r="N157" s="5"/>
-      <c r="O157" s="11"/>
-    </row>
-    <row r="158" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B158" s="20"/>
+      <c r="O157" s="4"/>
+    </row>
+    <row r="158" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B158" s="8"/>
       <c r="C158" s="1" t="s">
         <v>9</v>
       </c>
@@ -6207,12 +7600,12 @@
       <c r="N158" s="6">
         <v>2</v>
       </c>
-      <c r="O158" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="159" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B159" s="21"/>
+      <c r="O158" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B159" s="9"/>
       <c r="C159" s="3" t="s">
         <v>14</v>
       </c>
@@ -6235,10 +7628,10 @@
       <c r="N159" s="5">
         <v>2</v>
       </c>
-      <c r="O159" s="11"/>
-    </row>
-    <row r="160" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B160" s="20"/>
+      <c r="O159" s="4"/>
+    </row>
+    <row r="160" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B160" s="8"/>
       <c r="C160" s="1" t="s">
         <v>19</v>
       </c>
@@ -6257,10 +7650,10 @@
       <c r="N160" s="6">
         <v>1</v>
       </c>
-      <c r="O160" s="10"/>
-    </row>
-    <row r="161" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B161" s="21"/>
+      <c r="O160" s="2"/>
+    </row>
+    <row r="161" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B161" s="9"/>
       <c r="C161" s="3" t="s">
         <v>11</v>
       </c>
@@ -6277,10 +7670,10 @@
       <c r="L161" s="5"/>
       <c r="M161" s="4"/>
       <c r="N161" s="5"/>
-      <c r="O161" s="11"/>
-    </row>
-    <row r="162" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B162" s="20"/>
+      <c r="O161" s="4"/>
+    </row>
+    <row r="162" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B162" s="8"/>
       <c r="C162" s="1" t="s">
         <v>51</v>
       </c>
@@ -6297,10 +7690,10 @@
       <c r="N162" s="6">
         <v>1</v>
       </c>
-      <c r="O162" s="10"/>
-    </row>
-    <row r="163" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B163" s="21"/>
+      <c r="O162" s="2"/>
+    </row>
+    <row r="163" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B163" s="9"/>
       <c r="C163" s="3" t="s">
         <v>8</v>
       </c>
@@ -6323,12 +7716,12 @@
       <c r="N163" s="5">
         <v>1</v>
       </c>
-      <c r="O163" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="164" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B164" s="20"/>
+      <c r="O163" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B164" s="8"/>
       <c r="C164" s="1" t="s">
         <v>20</v>
       </c>
@@ -6365,12 +7758,12 @@
       <c r="N164" s="6">
         <v>18</v>
       </c>
-      <c r="O164" s="10">
+      <c r="O164" s="2">
         <v>24</v>
       </c>
     </row>
-    <row r="165" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B165" s="21"/>
+    <row r="165" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B165" s="9"/>
       <c r="C165" s="3" t="s">
         <v>50</v>
       </c>
@@ -6389,10 +7782,10 @@
       <c r="L165" s="5"/>
       <c r="M165" s="4"/>
       <c r="N165" s="5"/>
-      <c r="O165" s="11"/>
-    </row>
-    <row r="166" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B166" s="20"/>
+      <c r="O165" s="4"/>
+    </row>
+    <row r="166" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B166" s="8"/>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
@@ -6413,12 +7806,12 @@
       <c r="L166" s="6"/>
       <c r="M166" s="2"/>
       <c r="N166" s="6"/>
-      <c r="O166" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="167" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B167" s="21"/>
+      <c r="O166" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B167" s="9"/>
       <c r="C167" s="3" t="s">
         <v>18</v>
       </c>
@@ -6455,12 +7848,12 @@
       <c r="N167" s="5">
         <v>2</v>
       </c>
-      <c r="O167" s="11">
+      <c r="O167" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B168" s="20"/>
+    <row r="168" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B168" s="8"/>
       <c r="C168" s="1" t="s">
         <v>45</v>
       </c>
@@ -6497,12 +7890,12 @@
       <c r="N168" s="6">
         <v>13</v>
       </c>
-      <c r="O168" s="10">
+      <c r="O168" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B169" s="21"/>
+    <row r="169" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B169" s="9"/>
       <c r="C169" s="3" t="s">
         <v>12</v>
       </c>
@@ -6529,10 +7922,10 @@
       </c>
       <c r="M169" s="4"/>
       <c r="N169" s="5"/>
-      <c r="O169" s="11"/>
-    </row>
-    <row r="170" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B170" s="20"/>
+      <c r="O169" s="4"/>
+    </row>
+    <row r="170" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B170" s="8"/>
       <c r="C170" s="1" t="s">
         <v>2</v>
       </c>
@@ -6569,12 +7962,12 @@
       <c r="N170" s="6">
         <v>2</v>
       </c>
-      <c r="O170" s="10">
+      <c r="O170" s="2">
         <v>7</v>
       </c>
     </row>
-    <row r="171" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B171" s="21"/>
+    <row r="171" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B171" s="9"/>
       <c r="C171" s="3" t="s">
         <v>15</v>
       </c>
@@ -6591,10 +7984,10 @@
       <c r="L171" s="5"/>
       <c r="M171" s="4"/>
       <c r="N171" s="5"/>
-      <c r="O171" s="11"/>
-    </row>
-    <row r="172" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B172" s="20"/>
+      <c r="O171" s="4"/>
+    </row>
+    <row r="172" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B172" s="8"/>
       <c r="C172" s="1" t="s">
         <v>38</v>
       </c>
@@ -6631,12 +8024,12 @@
       <c r="N172" s="6">
         <v>91</v>
       </c>
-      <c r="O172" s="10">
+      <c r="O172" s="2">
         <v>93</v>
       </c>
     </row>
-    <row r="173" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B173" s="21"/>
+    <row r="173" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B173" s="9"/>
       <c r="C173" s="3" t="s">
         <v>7</v>
       </c>
@@ -6653,10 +8046,10 @@
       <c r="L173" s="5"/>
       <c r="M173" s="4"/>
       <c r="N173" s="5"/>
-      <c r="O173" s="11"/>
-    </row>
-    <row r="174" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B174" s="20"/>
+      <c r="O173" s="4"/>
+    </row>
+    <row r="174" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B174" s="8"/>
       <c r="C174" s="1" t="s">
         <v>47</v>
       </c>
@@ -6685,10 +8078,10 @@
       <c r="N174" s="6">
         <v>1</v>
       </c>
-      <c r="O174" s="10"/>
-    </row>
-    <row r="175" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B175" s="21"/>
+      <c r="O174" s="2"/>
+    </row>
+    <row r="175" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B175" s="9"/>
       <c r="C175" s="3" t="s">
         <v>6</v>
       </c>
@@ -6717,46 +8110,53 @@
       <c r="N175" s="5">
         <v>1</v>
       </c>
-      <c r="O175" s="11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="176" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B176" s="22"/>
-      <c r="C176" s="12" t="s">
+      <c r="O175" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B176" s="13"/>
+      <c r="C176" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="D176" s="13">
-        <v>2</v>
-      </c>
-      <c r="E176" s="14">
-        <v>1</v>
-      </c>
-      <c r="F176" s="13"/>
-      <c r="G176" s="14">
-        <v>1</v>
-      </c>
-      <c r="H176" s="13">
-        <v>1</v>
-      </c>
-      <c r="I176" s="14"/>
-      <c r="J176" s="13">
-        <v>1</v>
-      </c>
-      <c r="K176" s="14">
-        <v>1</v>
-      </c>
-      <c r="L176" s="13">
-        <v>2</v>
-      </c>
-      <c r="M176" s="14">
-        <v>1</v>
-      </c>
-      <c r="N176" s="13"/>
-      <c r="O176" s="15"/>
+      <c r="D176" s="15">
+        <v>2</v>
+      </c>
+      <c r="E176" s="16">
+        <v>1</v>
+      </c>
+      <c r="F176" s="15"/>
+      <c r="G176" s="16">
+        <v>1</v>
+      </c>
+      <c r="H176" s="15">
+        <v>1</v>
+      </c>
+      <c r="I176" s="16"/>
+      <c r="J176" s="15">
+        <v>1</v>
+      </c>
+      <c r="K176" s="16">
+        <v>1</v>
+      </c>
+      <c r="L176" s="15">
+        <v>2</v>
+      </c>
+      <c r="M176" s="16">
+        <v>1</v>
+      </c>
+      <c r="N176" s="15"/>
+      <c r="O176" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="5">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+  </tableParts>
 </worksheet>
 </file>
 
